--- a/tools/xlsform_samples/DistTherm.xlsx
+++ b/tools/xlsform_samples/DistTherm.xlsx
@@ -2050,7 +2050,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>distress (sum_coded) - Distress thermometer rating (0–10). Single item.</t>
+          <t>distress (sum_coded) - Distress thermometer rating (0-10). Single item.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>practical (sum_coded) - Practical problems endorsed (0–5).</t>
+          <t>practical (sum_coded) - Practical problems endorsed (0-5).</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>family (sum_coded) - Family problems endorsed (0–3).</t>
+          <t>family (sum_coded) - Family problems endorsed (0-3).</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>emotional (sum_coded) - Emotional problems endorsed (0–6).</t>
+          <t>emotional (sum_coded) - Emotional problems endorsed (0-6).</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>spiritual (sum_coded) - Spiritual/religious concerns endorsed (0–1).</t>
+          <t>spiritual (sum_coded) - Spiritual/religious concerns endorsed (0-1).</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>physical (sum_coded) - Physical problems endorsed (0–21).</t>
+          <t>physical (sum_coded) - Physical problems endorsed (0-21).</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>problem_total (sum_coded) - Total problems endorsed (0–36).</t>
+          <t>problem_total (sum_coded) - Total problems endorsed (0-36).</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>

--- a/tools/xlsform_samples/DistTherm.xlsx
+++ b/tools/xlsform_samples/DistTherm.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="43" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -2010,264 +2010,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DistTherm_scoring</t>
+          <t>DistTherm_distress</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Computed Scores</t>
+          <t>distress (sum_coded) - Distress thermometer rating (0-10). Single item.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>${distress}</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>DistTherm_distress</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>distress (sum_coded) - Distress thermometer rating (0-10). Single item.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>${distress}</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>DistTherm_practical</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>practical (sum_coded) - Practical problems endorsed (0-5).</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>${grid_practical_1} + ${grid_practical_2} + ${grid_practical_3} + ${grid_practical_4} + ${grid_practical_5}</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>DistTherm_family</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>family (sum_coded) - Family problems endorsed (0-3).</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>${grid_family_1} + ${grid_family_2} + ${grid_family_3}</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>DistTherm_emotional</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>emotional (sum_coded) - Emotional problems endorsed (0-6).</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>${grid_emotional_1} + ${grid_emotional_2} + ${grid_emotional_3} + ${grid_emotional_4} + ${grid_emotional_5} + ${grid_emotional_6}</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>DistTherm_spiritual</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>spiritual (sum_coded) - Spiritual/religious concerns endorsed (0-1).</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>${grid_spiritual_1}</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>DistTherm_physical</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>physical (sum_coded) - Physical problems endorsed (0-21).</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>${grid_physical_1} + ${grid_physical_2} + ${grid_physical_3} + ${grid_physical_4} + ${grid_physical_5} + ${grid_physical_6} + ${grid_physical_7} + ${grid_physical_8} + ${grid_physical_9} + ${grid_physical_10} + ${grid_physical_11} + ${grid_physical_12} + ${grid_physical_13} + ${grid_physical_14} + ${grid_physical_15} + ${grid_physical_16} + ${grid_physical_17} + ${grid_physical_18} + ${grid_physical_19} + ${grid_physical_20} + ${grid_physical_21}</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>DistTherm_problem_total</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>problem_total (sum_coded) - Total problems endorsed (0-36).</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>${grid_practical_1} + ${grid_practical_2} + ${grid_practical_3} + ${grid_practical_4} + ${grid_practical_5} + ${grid_family_1} + ${grid_family_2} + ${grid_family_3} + ${grid_emotional_1} + ${grid_emotional_2} + ${grid_emotional_3} + ${grid_emotional_4} + ${grid_emotional_5} + ${grid_emotional_6} + ${grid_spiritual_1} + ${grid_physical_1} + ${grid_physical_2} + ${grid_physical_3} + ${grid_physical_4} + ${grid_physical_5} + ${grid_physical_6} + ${grid_physical_7} + ${grid_physical_8} + ${grid_physical_9} + ${grid_physical_10} + ${grid_physical_11} + ${grid_physical_12} + ${grid_physical_13} + ${grid_physical_14} + ${grid_physical_15} + ${grid_physical_16} + ${grid_physical_17} + ${grid_physical_18} + ${grid_physical_19} + ${grid_physical_20} + ${grid_physical_21}</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>DistTherm_scoring</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/DistTherm.xlsx
+++ b/tools/xlsform_samples/DistTherm.xlsx
@@ -2301,7 +2301,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
